--- a/app/content/sichou.xlsx
+++ b/app/content/sichou.xlsx
@@ -1365,7 +1365,7 @@
         <v>敕令责问</v>
       </c>
       <c r="C2" t="str">
-        <v>威</v>
+        <v>势</v>
       </c>
       <c r="D2" t="str">
         <v>亮出御批敕令，厉声诘其渎职拦官之罪。</v>
@@ -1376,8 +1376,8 @@
       <c r="F2">
         <v>4</v>
       </c>
-      <c r="G2">
-        <v>3</v>
+      <c r="G2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -1388,7 +1388,7 @@
         <v>冷眼威压</v>
       </c>
       <c r="C3" t="str">
-        <v>威</v>
+        <v>隐</v>
       </c>
       <c r="D3" t="str">
         <v>不发一言，只冷冷盯着他的笑。</v>
@@ -1411,7 +1411,7 @@
         <v>官场人情</v>
       </c>
       <c r="C4" t="str">
-        <v>利</v>
+        <v>势</v>
       </c>
       <c r="D4" t="str">
         <v>抬出刑部旧谊，递一句台阶。</v>
@@ -1422,8 +1422,8 @@
       <c r="F4">
         <v>2</v>
       </c>
-      <c r="G4">
-        <v>1</v>
+      <c r="G4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -1434,7 +1434,7 @@
         <v>许以好处</v>
       </c>
       <c r="C5" t="str">
-        <v>利</v>
+        <v>器</v>
       </c>
       <c r="D5" t="str">
         <v>暗示事成之后，保他考绩无忧。</v>
@@ -1457,7 +1457,7 @@
         <v>雨中体恤</v>
       </c>
       <c r="C6" t="str">
-        <v>情</v>
+        <v>策</v>
       </c>
       <c r="D6" t="str">
         <v>看他淋在雨里，递一句「辛苦」。</v>
@@ -1468,8 +1468,8 @@
       <c r="F6">
         <v>2</v>
       </c>
-      <c r="G6">
-        <v>1</v>
+      <c r="G6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1480,7 +1480,7 @@
         <v>问其家小</v>
       </c>
       <c r="C7" t="str">
-        <v>情</v>
+        <v>隐</v>
       </c>
       <c r="D7" t="str">
         <v>问他家中可有妻儿，靠谁过活。</v>
@@ -1503,7 +1503,7 @@
         <v>晓明规矩</v>
       </c>
       <c r="C8" t="str">
-        <v>理</v>
+        <v>策</v>
       </c>
       <c r="D8" t="str">
         <v>与他细论贡院出入规制、勘验条陈。</v>
@@ -1526,7 +1526,7 @@
         <v>条分利害</v>
       </c>
       <c r="C9" t="str">
-        <v>理</v>
+        <v>策</v>
       </c>
       <c r="D9" t="str">
         <v>替他算清：阻拦钦差，是灭门的罪。</v>
@@ -1537,8 +1537,8 @@
       <c r="F9">
         <v>4</v>
       </c>
-      <c r="G9">
-        <v>3</v>
+      <c r="G9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1548,6 +1548,9 @@
       <c r="B10" t="str">
         <v>江西银票</v>
       </c>
+      <c r="C10" t="str">
+        <v>器</v>
+      </c>
       <c r="D10" t="str">
         <v>对局中出示：宁王宗族专属银票——见者无不色变。</v>
       </c>
@@ -1568,6 +1571,9 @@
       <c r="B11" t="str">
         <v>军饷底册</v>
       </c>
+      <c r="C11" t="str">
+        <v>器</v>
+      </c>
       <c r="D11" t="str">
         <v>对局中使用：虚兵两百一十六名的铁账，看一眼就火大。（+3）</v>
       </c>
@@ -1588,6 +1594,9 @@
       <c r="B12" t="str">
         <v>倭文密信</v>
       </c>
+      <c r="C12" t="str">
+        <v>器</v>
+      </c>
       <c r="D12" t="str">
         <v>对局中掷出：夹着桑皮纸的倭人私信，掷出即破伪。</v>
       </c>
@@ -1608,6 +1617,9 @@
       <c r="B13" t="str">
         <v>空白官印</v>
       </c>
+      <c r="C13" t="str">
+        <v>器</v>
+      </c>
       <c r="D13" t="str">
         <v>对局中使用：无备案御用官印——下一言即是「宫里的意思」。（成术+3）</v>
       </c>
@@ -1628,6 +1640,9 @@
       <c r="B14" t="str">
         <v>桑皮纸残页</v>
       </c>
+      <c r="C14" t="str">
+        <v>器</v>
+      </c>
       <c r="D14" t="str">
         <v>对局中使用：与宫中御用密信同纹——翻检线索，再抽两张牌。</v>
       </c>
@@ -1648,6 +1663,9 @@
       <c r="B15" t="str">
         <v>暗纹云锦</v>
       </c>
+      <c r="C15" t="str">
+        <v>器</v>
+      </c>
       <c r="D15" t="str">
         <v>对局中亮出：锦底金线帝王私纹——深宫的爪牙见了都要跪。</v>
       </c>
@@ -1668,8 +1686,11 @@
       <c r="B16" t="str">
         <v>牙人贾三</v>
       </c>
+      <c r="C16" t="str">
+        <v>势</v>
+      </c>
       <c r="D16" t="str">
-        <v>携带：利牌 +1。游走官商码头三十年，什么都卖，什么都买。</v>
+        <v>携带：器牌 +1。游走官商码头三十年，什么都卖，什么都买。</v>
       </c>
       <c r="E16" t="str">
         <v>「大人要什么？人，话，还是命？——小人只收现银。」</v>
@@ -1688,8 +1709,11 @@
       <c r="B17" t="str">
         <v>织女阿桃</v>
       </c>
+      <c r="C17" t="str">
+        <v>势</v>
+      </c>
       <c r="D17" t="str">
-        <v>携带：情牌 +1。失地的农户，织坊的女工，眼睛比谁都亮。</v>
+        <v>携带：策牌 +1。失地的农户，织坊的女工，眼睛比谁都亮。</v>
       </c>
       <c r="E17" t="str">
         <v>「堤下黑土，我们踩着长大，我们认得出。」</v>
@@ -1708,8 +1732,11 @@
       <c r="B18" t="str">
         <v>账房吕思远</v>
       </c>
+      <c r="C18" t="str">
+        <v>势</v>
+      </c>
       <c r="D18" t="str">
-        <v>携带：理牌 +1。三十年的账，烂熟于心。</v>
+        <v>携带：器牌 +1。三十年的账，烂熟于心。</v>
       </c>
       <c r="E18" t="str">
         <v>他唯一没记的那笔账，是拿命换的沉默。</v>
@@ -1728,8 +1755,11 @@
       <c r="B19" t="str">
         <v>亲兵陈虎</v>
       </c>
+      <c r="C19" t="str">
+        <v>势</v>
+      </c>
       <c r="D19" t="str">
-        <v>携带：威牌 +1。押过军械、送过凿具的诚实人。</v>
+        <v>携带：势牌 +1。押过军械、送过凿具的诚实人。</v>
       </c>
       <c r="E19" t="str">
         <v>他说的每一句都属实。除了他不敢说的那些。</v>
@@ -1748,8 +1778,11 @@
       <c r="B20" t="str">
         <v>太监刘小三</v>
       </c>
+      <c r="C20" t="str">
+        <v>势</v>
+      </c>
       <c r="D20" t="str">
-        <v>携带：威牌 +1，气力上限 +2。无靠山的随堂太监，一肚子火。</v>
+        <v>携带：势牌 +1，气力上限 +2。无靠山的随堂太监，一肚子火。</v>
       </c>
       <c r="E20" t="str">
         <v>「小人无朝堂靠山——所以小人，什么都不怕。」</v>
@@ -1768,6 +1801,9 @@
       <c r="B21" t="str">
         <v>碎银十两</v>
       </c>
+      <c r="C21" t="str">
+        <v>器</v>
+      </c>
       <c r="D21" t="str">
         <v>资源卡：翻到即入钱袋。</v>
       </c>
@@ -1788,6 +1824,9 @@
       <c r="B22" t="str">
         <v>商银五十两</v>
       </c>
+      <c r="C22" t="str">
+        <v>器</v>
+      </c>
       <c r="D22" t="str">
         <v>资源卡：翻到即入钱袋。</v>
       </c>
@@ -1807,6 +1846,9 @@
       </c>
       <c r="B23" t="str">
         <v>官银百两</v>
+      </c>
+      <c r="C23" t="str">
+        <v>器</v>
       </c>
       <c r="D23" t="str">
         <v>资源卡：翻到即入钱袋。</v>
@@ -2097,7 +2139,7 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>理,威,理,理,威,情,利</v>
+        <v>策,势,策,隐,策,势,策</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -2129,7 +2171,7 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>10/10</v>
+        <v>10/8</v>
       </c>
       <c r="H3" t="str">
         <v>y_feng,y_xiao,y_zhen,y_feng,y_zhen,y_xiao</v>
